--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486492_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486492_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9178</v>
+        <v>3.4804</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6415</v>
+        <v>4.865</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7236</v>
+        <v>-1.3846</v>
       </c>
       <c r="G2" t="n">
         <v>5.3132</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0055</v>
+        <v>-1.4429</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2329</v>
+        <v>-1.0094</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7726</v>
+        <v>-0.4335</v>
       </c>
       <c r="V2" t="n">
         <v>-1.695</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0108</v>
+        <v>1.9906</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5447</v>
+        <v>0.4152</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5339</v>
+        <v>1.5754</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3896</v>
+        <v>-0.2309</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0527</v>
+        <v>0.1093</v>
       </c>
       <c r="I3" t="n">
-        <v>1.663</v>
+        <v>-0.3403</v>
       </c>
       <c r="J3" t="n">
-        <v>0.97</v>
+        <v>-0.0236</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.6454</v>
+        <v>0.1277</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6154</v>
+        <v>-0.1514</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3596</v>
+        <v>-0.2073</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5927</v>
+        <v>-0.0184</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9523</v>
+        <v>-0.1889</v>
       </c>
       <c r="P3" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3598</v>
+        <v>-0.0835</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5754</v>
+        <v>-0.1262</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2156</v>
+        <v>0.0427</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8902</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1501</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6168</v>
+        <v>1.691</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1436</v>
+        <v>3.6565</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7604</v>
+        <v>-1.9654</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2309</v>
+        <v>-0.3896</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1093</v>
+        <v>-2.0527</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3403</v>
+        <v>1.663</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0236</v>
+        <v>0.97</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1277</v>
+        <v>-2.6454</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1514</v>
+        <v>3.6154</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2073</v>
+        <v>-1.3596</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0184</v>
+        <v>0.5927</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1889</v>
+        <v>-1.9523</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4574</v>
+        <v>-0.6796</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-1.4637</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2276</v>
+        <v>0.7841</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.8902</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5649999999999999</v>
+        <v>4.1501</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3378</v>
+        <v>0.6249</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8509</v>
+        <v>1.2921</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.513</v>
+        <v>-0.6672</v>
       </c>
       <c r="G5" t="n">
         <v>0.2019</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1338</v>
+        <v>0.4209</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0791</v>
+        <v>0.5203</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0547</v>
+        <v>-0.0994</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5204</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5429</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0145</v>
+        <v>1.7867</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4716</v>
+        <v>-1.7235</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0858</v>
+        <v>1.0887</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3232</v>
+        <v>1.0281</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.0606</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7736</v>
+        <v>3.1909</v>
       </c>
       <c r="K6" t="n">
-        <v>1.375</v>
+        <v>1.4115</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3985</v>
+        <v>1.7794</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6878</v>
+        <v>-2.1022</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0519</v>
+        <v>-0.3834</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6359</v>
+        <v>-1.7188</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.8276</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3735</v>
+        <v>-0.0907</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7367</v>
+        <v>-0.5119</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3632</v>
+        <v>0.4212</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1745</v>
+        <v>-0.9347</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1745</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5687</v>
+        <v>-0.4956</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3397</v>
+        <v>0.026</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9084</v>
+        <v>-0.5216</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0887</v>
+        <v>2.2646</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0281</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0606</v>
+        <v>2.879</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1909</v>
+        <v>3.3907</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4115</v>
+        <v>-0.7601</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7794</v>
+        <v>4.1509</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1022</v>
+        <v>-1.1261</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3834</v>
+        <v>0.1457</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7188</v>
+        <v>-1.2718</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7227</v>
+        <v>-1.1077</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9589</v>
+        <v>-1.1897</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2362</v>
+        <v>0.082</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9347</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.193</v>
+        <v>-0.7433</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0858</v>
+        <v>-1.4615</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1072</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2646</v>
+        <v>2.0858</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6143999999999999</v>
+        <v>1.3232</v>
       </c>
       <c r="I8" t="n">
-        <v>2.879</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3907</v>
+        <v>2.7736</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7601</v>
+        <v>1.375</v>
       </c>
       <c r="L8" t="n">
-        <v>4.1509</v>
+        <v>1.3985</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1261</v>
+        <v>-0.6878</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1457</v>
+        <v>-0.0519</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2718</v>
+        <v>-0.6359</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0875</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8051</v>
+        <v>0.173</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3014</v>
+        <v>0.2896</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5036</v>
+        <v>-0.1166</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1745</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2594</v>
+        <v>-1.8451</v>
       </c>
       <c r="E9" t="n">
         <v>-2.5609</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3015</v>
+        <v>0.7159</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6766</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.178</v>
+        <v>-0.4077</v>
       </c>
       <c r="T9" t="n">
         <v>-1.2329</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4109</v>
+        <v>0.8253</v>
       </c>
       <c r="V9" t="n">
         <v>1.6743</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6874</v>
+        <v>-2.042</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6933</v>
+        <v>-2.1403</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0059</v>
+        <v>0.0984</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5011</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2912</v>
+        <v>-0.0634</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3509</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6421</v>
+        <v>0.7345</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.997</v>
+        <v>-3.0381</v>
       </c>
       <c r="E11" t="n">
         <v>-3.3451</v>
       </c>
       <c r="F11" t="n">
-        <v>0.348</v>
+        <v>0.3069</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0958</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2912</v>
+        <v>-0.3323</v>
       </c>
       <c r="T11" t="n">
         <v>0.0601</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3513</v>
+        <v>-0.3924</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3651999999999997</v>
+        <v>-0.3140000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.533599999999999</v>
+        <v>2.5337</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8987</v>
+        <v>-2.8475</v>
       </c>
       <c r="G12" t="n">
         <v>4.0602</v>
       </c>
       <c r="H12" t="n">
-        <v>2.569900000000001</v>
+        <v>2.5699</v>
       </c>
       <c r="I12" t="n">
         <v>1.4899</v>
@@ -1372,13 +1372,13 @@
         <v>11.0288</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.902100000000001</v>
+        <v>-8.902099999999999</v>
       </c>
       <c r="N12" t="n">
         <v>0.6365000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.538599999999999</v>
+        <v>-9.538600000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-9.999999999976694e-05</v>
@@ -1390,28 +1390,28 @@
         <v>11.9626</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.6652</v>
+        <v>-3.6139</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.4615</v>
+        <v>-5.4617</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7964</v>
+        <v>1.8479</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7601</v>
+        <v>-0.7600999999999998</v>
       </c>
       <c r="W12" t="n">
         <v>6.995799999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.756</v>
+        <v>-7.755999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.129</v>
+        <v>4.5553</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9606</v>
+        <v>4.7905</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1683</v>
+        <v>-0.2352</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4898</v>
+        <v>1.6297</v>
       </c>
       <c r="H13" t="n">
-        <v>1.551</v>
+        <v>0.7603</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9388</v>
+        <v>0.8694</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4485</v>
+        <v>4.3687</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5544</v>
+        <v>1.229</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8941</v>
+        <v>3.1397</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0413</v>
+        <v>-2.739</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0033</v>
+        <v>-0.4688</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0446</v>
+        <v>-2.2703</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5516</v>
+        <v>0.1006</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5997</v>
+        <v>-0.7931</v>
       </c>
       <c r="U13" t="n">
-        <v>0.952</v>
+        <v>0.8937</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5649999999999999</v>
+        <v>2.8249</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="X13" t="n">
         <v>-0.5649999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4955</v>
+        <v>4.3236</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0082</v>
+        <v>2.4018</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5125999999999999</v>
+        <v>1.9217</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6297</v>
+        <v>3.4898</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7603</v>
+        <v>1.551</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8694</v>
+        <v>1.9388</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3687</v>
+        <v>3.4485</v>
       </c>
       <c r="K14" t="n">
-        <v>1.229</v>
+        <v>1.5544</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1397</v>
+        <v>1.8941</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.739</v>
+        <v>0.0413</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4688</v>
+        <v>-0.0033</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2703</v>
+        <v>0.0446</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9591</v>
+        <v>0.7463</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5754</v>
+        <v>0.0409</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6163</v>
+        <v>0.7054</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8249</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3899</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.5649999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8029</v>
+        <v>2.3639</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8384</v>
+        <v>2.0746</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0355</v>
+        <v>0.2893</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4784</v>
+        <v>0.0833</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0218</v>
+        <v>-2.9862</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4566</v>
+        <v>3.0695</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7731</v>
+        <v>2.7888</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8879</v>
+        <v>-2.551</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1147</v>
+        <v>5.3398</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7053</v>
+        <v>-2.7056</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1339</v>
+        <v>-0.4353</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5714</v>
+        <v>-2.2703</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6525</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2384</v>
+        <v>-0.3061</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0911</v>
+        <v>-0.7991</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1472</v>
+        <v>0.493</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3904</v>
+        <v>2.8042</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5204</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5893</v>
+        <v>0.8434</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5158</v>
+        <v>1.2796</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0735</v>
+        <v>-0.4362</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0833</v>
+        <v>-1.4784</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.9862</v>
+        <v>-1.0218</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0695</v>
+        <v>-0.4566</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7888</v>
+        <v>-0.7731</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.551</v>
+        <v>-0.8879</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3398</v>
+        <v>0.1147</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7056</v>
+        <v>-0.7053</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4353</v>
+        <v>-0.1339</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2703</v>
+        <v>-0.5714</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0807</v>
+        <v>1.2789</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3579</v>
+        <v>0.5324</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2772</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8042</v>
+        <v>0.3904</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>1.5204</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5443</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>C. BARTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0605</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0466</v>
+        <v>-1.8687</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0139</v>
+        <v>1.7777</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8107</v>
+        <v>1.7943</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3528</v>
+        <v>0.4013</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1634</v>
+        <v>1.3929</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9226</v>
+        <v>0.9361</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7696</v>
+        <v>0.0547</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>0.8813</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7333</v>
+        <v>0.8582</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4169</v>
+        <v>0.3466</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3164</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1199</v>
+        <v>0.7249</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0769</v>
+        <v>0.4579</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1968</v>
+        <v>0.2671</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. BARTON</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5417</v>
+        <v>-0.4574</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9804</v>
+        <v>-0.3818</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4387</v>
+        <v>-0.0756</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7943</v>
+        <v>-0.8107</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4013</v>
+        <v>0.3528</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3929</v>
+        <v>-1.1634</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9361</v>
+        <v>0.9226</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0547</v>
+        <v>0.7696</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8813</v>
+        <v>0.153</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8582</v>
+        <v>-1.7333</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3466</v>
+        <v>-0.4169</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5116000000000001</v>
+        <v>-1.3164</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.6101</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2741</v>
+        <v>-0.277</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3461</v>
+        <v>-0.4122</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.1352</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1811</v>
+        <v>-1.6242</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1115</v>
+        <v>-0.9998</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0696</v>
+        <v>-0.6244</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5699</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.714</v>
+        <v>0.271</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1935</v>
+        <v>0.6387</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3252</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6932</v>
+        <v>-1.9572</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9936</v>
+        <v>-1.6583</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6996</v>
+        <v>-0.2989</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9964</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0019</v>
+        <v>-0.2659</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3377</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3289</v>
+        <v>0.0718</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9318</v>
+        <v>-3.163</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.775</v>
+        <v>-1.222</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1568</v>
+        <v>-1.941</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1617</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>0.925</v>
+        <v>0.6937</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3942</v>
+        <v>-0.0529</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5308</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5649999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6782</v>
+        <v>-3.8632</v>
       </c>
       <c r="E23" t="n">
         <v>-1.5172</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1611</v>
+        <v>-2.346</v>
       </c>
       <c r="G23" t="n">
         <v>-2.475</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8837</v>
+        <v>0.6988</v>
       </c>
       <c r="T23" t="n">
         <v>-0.0649</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9486</v>
+        <v>0.7637</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8695</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3652000000000002</v>
+        <v>0.3653000000000004</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8987</v>
+        <v>2.898700000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-2.5336</v>
@@ -2326,13 +2326,13 @@
         <v>11.9629</v>
       </c>
       <c r="S24" t="n">
-        <v>3.665</v>
+        <v>3.665199999999999</v>
       </c>
       <c r="T24" t="n">
         <v>-1.7964</v>
       </c>
       <c r="U24" t="n">
-        <v>5.4615</v>
+        <v>5.4616</v>
       </c>
       <c r="V24" t="n">
         <v>0.7599999999999998</v>
